--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -457,7 +457,7 @@
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -468,7 +468,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
@@ -484,8 +484,12 @@
       <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="6">
+        <f>B24</f>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <f xml:space="preserve"> B3</f>
         <v>700000</v>
@@ -501,7 +505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <f xml:space="preserve"> A3 + B4-C4</f>
         <v>700000</v>
@@ -511,7 +515,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A23" si="0" xml:space="preserve"> A4 + B5-C5</f>
         <v>700000</v>
@@ -521,7 +525,7 @@
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -531,7 +535,7 @@
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -541,7 +545,7 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -551,7 +555,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -561,7 +565,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -571,7 +575,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -581,7 +585,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -591,7 +595,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -601,7 +605,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -611,7 +615,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -621,7 +625,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>قهوه سیگار تخم مرغ</t>
+  </si>
+  <si>
+    <t>1405/07/13</t>
+  </si>
+  <si>
+    <t>سیگار بستنی</t>
   </si>
 </sst>
 </file>
@@ -454,6 +460,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18.25" customWidth="1"/>
     <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -486,7 +493,7 @@
       </c>
       <c r="H2" s="6">
         <f>B24</f>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -508,17 +515,23 @@
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <f xml:space="preserve"> A3 + B4-C4</f>
-        <v>700000</v>
-      </c>
-      <c r="B4" s="10"/>
+        <v>1100000</v>
+      </c>
+      <c r="B4" s="10">
+        <v>400000</v>
+      </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A23" si="0" xml:space="preserve"> A4 + B5-C5</f>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -528,7 +541,7 @@
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -538,7 +551,7 @@
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -548,7 +561,7 @@
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -558,7 +571,7 @@
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -568,7 +581,7 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -578,7 +591,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -588,7 +601,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -598,7 +611,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -608,7 +621,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -618,7 +631,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -628,7 +641,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -638,7 +651,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -648,7 +661,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -658,7 +671,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -668,7 +681,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -678,7 +691,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -688,7 +701,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -698,7 +711,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -709,7 +722,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -730,7 +743,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -177,7 +177,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -874,6 +896,14 @@
     <row r="84" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="85" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>سیگار بستنی</t>
+  </si>
+  <si>
+    <t>1405/07/16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیگار  </t>
   </si>
 </sst>
 </file>
@@ -177,14 +183,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -515,7 +514,7 @@
       </c>
       <c r="H2" s="6">
         <f>B24</f>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -553,17 +552,23 @@
     <row r="5" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A23" si="0" xml:space="preserve"> A4 + B5-C5</f>
-        <v>1100000</v>
-      </c>
-      <c r="B5" s="10"/>
+        <v>1200000</v>
+      </c>
+      <c r="B5" s="10">
+        <v>100000</v>
+      </c>
       <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -573,7 +578,7 @@
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -583,7 +588,7 @@
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -593,7 +598,7 @@
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -603,7 +608,7 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -613,7 +618,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -623,7 +628,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -633,7 +638,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -643,7 +648,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -653,7 +658,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -663,7 +668,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -673,7 +678,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -683,7 +688,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -693,7 +698,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -703,7 +708,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -713,7 +718,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -723,7 +728,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -733,7 +738,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -744,7 +749,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -765,7 +770,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>
@@ -897,10 +902,10 @@
     <row r="85" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="C26">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t xml:space="preserve">سیگار  </t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>سیگار تخم مرغ</t>
   </si>
 </sst>
 </file>
@@ -514,7 +520,7 @@
       </c>
       <c r="H2" s="6">
         <f>B24</f>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -568,17 +574,23 @@
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
-      </c>
-      <c r="B6" s="10"/>
+        <v>1887000</v>
+      </c>
+      <c r="B6" s="10">
+        <v>687000</v>
+      </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -588,7 +600,7 @@
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -598,7 +610,7 @@
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -608,7 +620,7 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -618,7 +630,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -628,7 +640,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -638,7 +650,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -648,7 +660,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -658,7 +670,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -668,7 +680,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -678,7 +690,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -688,7 +700,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -698,7 +710,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -708,7 +720,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -718,7 +730,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -728,7 +740,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -738,7 +750,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -749,7 +761,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -770,7 +782,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>سیگار تخم مرغ</t>
+  </si>
+  <si>
+    <t>1405/07/22</t>
+  </si>
+  <si>
+    <t>وجه</t>
   </si>
 </sst>
 </file>
@@ -590,17 +596,23 @@
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="C7" s="10">
+        <v>1800000</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -610,7 +622,7 @@
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -620,7 +632,7 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -630,7 +642,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -640,7 +652,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -650,7 +662,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -660,7 +672,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -670,7 +682,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -680,7 +692,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -690,7 +702,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -700,7 +712,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -710,7 +722,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -720,7 +732,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -730,7 +742,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -740,7 +752,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -750,7 +762,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -765,7 +777,7 @@
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
@@ -782,7 +794,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -525,8 +525,8 @@
         <v>5</v>
       </c>
       <c r="H2" s="6">
-        <f>B24</f>
-        <v>1887000</v>
+        <f>C26</f>
+        <v>87000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>وجه</t>
+  </si>
+  <si>
+    <t>1405/07/24</t>
+  </si>
+  <si>
+    <t>سیگار کرانچی</t>
   </si>
 </sst>
 </file>
@@ -526,7 +532,7 @@
       </c>
       <c r="H2" s="6">
         <f>C26</f>
-        <v>87000</v>
+        <v>447000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -612,17 +618,23 @@
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
-      </c>
-      <c r="B8" s="10"/>
+        <v>447000</v>
+      </c>
+      <c r="B8" s="10">
+        <v>360000</v>
+      </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="D8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -632,7 +644,7 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -642,7 +654,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -652,7 +664,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -662,7 +674,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -672,7 +684,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -682,7 +694,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -692,7 +704,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -702,7 +714,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -712,7 +724,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -722,7 +734,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -732,7 +744,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -742,7 +754,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -752,7 +764,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -762,7 +774,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -773,7 +785,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>1887000</v>
+        <v>2247000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -794,7 +806,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>سیگار کرانچی</t>
+  </si>
+  <si>
+    <t>1405/07/27</t>
+  </si>
+  <si>
+    <t>سیگار اسپرسو بستنی</t>
   </si>
 </sst>
 </file>
@@ -532,7 +538,7 @@
       </c>
       <c r="H2" s="6">
         <f>C26</f>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -634,17 +640,23 @@
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
-      </c>
-      <c r="B9" s="10"/>
+        <v>1043000</v>
+      </c>
+      <c r="B9" s="10">
+        <v>596000</v>
+      </c>
       <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="D9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -654,7 +666,7 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -664,7 +676,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -674,7 +686,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -684,7 +696,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -694,7 +706,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -704,7 +716,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -714,7 +726,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -724,7 +736,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -734,7 +746,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -744,7 +756,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -754,7 +766,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -764,7 +776,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -774,7 +786,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -785,7 +797,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>2247000</v>
+        <v>2843000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -806,7 +818,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>سیگار اسپرسو بستنی</t>
+  </si>
+  <si>
+    <t>1405/08/01</t>
+  </si>
+  <si>
+    <t>سیگار گازفندک</t>
   </si>
 </sst>
 </file>
@@ -538,7 +544,7 @@
       </c>
       <c r="H2" s="6">
         <f>C26</f>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -656,17 +662,23 @@
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
-      </c>
-      <c r="B10" s="10"/>
+        <v>1673000</v>
+      </c>
+      <c r="B10" s="10">
+        <v>630000</v>
+      </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -676,7 +688,7 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -686,7 +698,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -696,7 +708,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -706,7 +718,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -716,7 +728,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -726,7 +738,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -736,7 +748,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -746,7 +758,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -756,7 +768,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -766,7 +778,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -776,7 +788,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -786,7 +798,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -797,7 +809,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>2843000</v>
+        <v>3473000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -818,7 +830,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>سیگار گازفندک</t>
+  </si>
+  <si>
+    <t>1405/08/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیگار اسپرسو  </t>
   </si>
 </sst>
 </file>
@@ -544,7 +550,7 @@
       </c>
       <c r="H2" s="6">
         <f>C26</f>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -678,17 +684,23 @@
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
-      </c>
-      <c r="B11" s="10"/>
+        <v>2427000</v>
+      </c>
+      <c r="B11" s="10">
+        <v>754000</v>
+      </c>
       <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -698,7 +710,7 @@
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -708,7 +720,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -718,7 +730,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -728,7 +740,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -738,7 +750,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -748,7 +760,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -758,7 +770,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -768,7 +780,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -778,7 +790,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -788,7 +800,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -798,7 +810,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -809,7 +821,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>3473000</v>
+        <v>4227000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -830,7 +842,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>

--- a/customers/ali.xlsx
+++ b/customers/ali.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t xml:space="preserve">سیگار اسپرسو  </t>
+  </si>
+  <si>
+    <t>1405/08/08</t>
+  </si>
+  <si>
+    <t>سیگار اسپرسو</t>
   </si>
 </sst>
 </file>
@@ -550,7 +556,7 @@
       </c>
       <c r="H2" s="6">
         <f>C26</f>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -700,17 +706,23 @@
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
-      </c>
-      <c r="B12" s="10"/>
+        <v>2922000</v>
+      </c>
+      <c r="B12" s="10">
+        <v>495000</v>
+      </c>
       <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -720,7 +732,7 @@
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -730,7 +742,7 @@
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -740,7 +752,7 @@
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -750,7 +762,7 @@
     <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -760,7 +772,7 @@
     <row r="18" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -770,7 +782,7 @@
     <row r="19" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -780,7 +792,7 @@
     <row r="20" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -790,7 +802,7 @@
     <row r="21" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
@@ -800,7 +812,7 @@
     <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -810,7 +822,7 @@
     <row r="23" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -821,7 +833,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13">
         <f xml:space="preserve"> SUM(B3:B23)</f>
-        <v>4227000</v>
+        <v>4722000</v>
       </c>
       <c r="C24" s="13">
         <f xml:space="preserve"> SUM(C3:C23)</f>
@@ -842,7 +854,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14">
         <f>A23</f>
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>6</v>
